--- a/data/data_minerals/data_availability_marin.xlsx
+++ b/data/data_minerals/data_availability_marin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2440" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFE3B620-6845-46C1-B4CD-9FCABA397A71}"/>
+  <xr:revisionPtr revIDLastSave="2442" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ED8C0DA-D407-4C1E-8056-4989AA6362BE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -4054,15 +4054,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>18203</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>34853</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>213956</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>38527</xdr:rowOff>
+      <xdr:colOff>192789</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>30200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4085,8 +4085,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3345180" y="3703320"/>
-          <a:ext cx="6881456" cy="4930567"/>
+          <a:off x="3313147" y="4804409"/>
+          <a:ext cx="6849142" cy="4948347"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4096,6 +4096,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/data_minerals/data_availability_marin.xlsx
+++ b/data/data_minerals/data_availability_marin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2442" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ED8C0DA-D407-4C1E-8056-4989AA6362BE}"/>
+  <xr:revisionPtr revIDLastSave="2443" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCD23F2B-18A8-46A2-BC8F-5236DBFACE28}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -49467,7 +49467,7 @@
       </c>
       <c r="G15" s="3" t="str">
         <f>CALCULATION!L18</f>
-        <v>kt</v>
+        <v>t</v>
       </c>
       <c r="H15" s="75">
         <f>CALCULATION!M18</f>
@@ -51477,7 +51477,7 @@
         <v>11444304.932735426</v>
       </c>
       <c r="L18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M18">
         <v>2023</v>

--- a/data/data_minerals/data_availability_marin.xlsx
+++ b/data/data_minerals/data_availability_marin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2443" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCD23F2B-18A8-46A2-BC8F-5236DBFACE28}"/>
+  <xr:revisionPtr revIDLastSave="2453" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42B73E32-54A0-45FC-9F8B-39C1CCBBF5A3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -4098,10 +4098,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/data/data_minerals/data_availability_marin.xlsx
+++ b/data/data_minerals/data_availability_marin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2453" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42B73E32-54A0-45FC-9F8B-39C1CCBBF5A3}"/>
+  <xr:revisionPtr revIDLastSave="2469" documentId="13_ncr:1_{3B0093C0-0E66-4485-936E-AE5475C25BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7134185-E8D9-4B69-AECA-E79BFFA0292E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -57,8 +57,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={29665DF2-F391-4BAC-AAA5-A6680DD06A2D}</author>
+  </authors>
+  <commentList>
+    <comment ref="C30" authorId="0" shapeId="0" xr:uid="{29665DF2-F391-4BAC-AAA5-A6680DD06A2D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not in the energy transition vs roe results</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10410" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10445" uniqueCount="1119">
   <si>
     <t>Mineral</t>
   </si>
@@ -3508,7 +3526,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3676,8 +3694,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3739,6 +3763,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3886,7 +3916,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -3995,6 +4025,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Default" xfId="2" xr:uid="{591B0DA1-F9B2-49FD-B0E7-4673A2758C34}"/>
@@ -4096,6 +4127,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Marin PELLAN" id="{F3A6D0A1-9EE4-47D8-B0E3-03E9BCE78932}" userId="S::marin.pellan@polymtlus.ca::b769edc3-00f3-432c-88ea-f74fb5c6c1e4" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4359,6 +4396,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C30" dT="2025-08-04T23:17:26.08" personId="{F3A6D0A1-9EE4-47D8-B0E3-03E9BCE78932}" id="{29665DF2-F391-4BAC-AAA5-A6680DD06A2D}">
+    <text>Not in the energy transition vs roe results</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D875D3-3CEF-4138-8A32-CAA36467249A}">
   <sheetPr>
@@ -48949,8 +48994,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D7BBB0-1678-4D93-9211-683284961981}">
-  <dimension ref="A1:H39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D7BBB0-1678-4D93-9211-683284961981}">
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -48963,7 +49008,7 @@
     <col min="8" max="8" width="5.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="str">
         <f>CALCULATION!A1</f>
         <v>Z</v>
@@ -48995,7 +49040,7 @@
         <v>Year</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>CALCULATION!A2</f>
         <v>13</v>
@@ -49028,8 +49073,14 @@
         <f>CALCULATION!M2</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>CALCULATION!A3</f>
         <v>33</v>
@@ -49062,8 +49113,14 @@
         <f>CALCULATION!M3</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>CALCULATION!A4</f>
         <v>5</v>
@@ -49096,8 +49153,14 @@
         <f>CALCULATION!M4</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>CALCULATION!A5</f>
         <v>48</v>
@@ -49130,8 +49193,14 @@
         <f>CALCULATION!M5</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>CALCULATION!A6</f>
         <v>24</v>
@@ -49164,8 +49233,14 @@
         <f>CALCULATION!M6</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="L6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>CALCULATION!A7</f>
         <v>27</v>
@@ -49198,8 +49273,14 @@
         <f>CALCULATION!M7</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>CALCULATION!A8</f>
         <v>29</v>
@@ -49232,8 +49313,14 @@
         <f>CALCULATION!M8</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="L8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>CALCULATION!A9</f>
         <v>66</v>
@@ -49266,8 +49353,14 @@
         <f>CALCULATION!M9</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="L9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>CALCULATION!A12</f>
         <v>31</v>
@@ -49300,8 +49393,14 @@
         <f>CALCULATION!M12</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="L10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>CALCULATION!A13</f>
         <v>-</v>
@@ -49333,8 +49432,14 @@
         <f>CALCULATION!M13</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>CALCULATION!A15</f>
         <v>49</v>
@@ -49367,8 +49472,14 @@
         <f>CALCULATION!M15</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>11</v>
+      </c>
+      <c r="L12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>CALCULATION!A16</f>
         <v>77</v>
@@ -49401,8 +49512,14 @@
         <f>CALCULATION!M16</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="L13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>CALCULATION!A17</f>
         <v>57</v>
@@ -49435,8 +49552,14 @@
         <f>CALCULATION!M17</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>13</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>CALCULATION!A18</f>
         <v>82</v>
@@ -49469,8 +49592,14 @@
         <f>CALCULATION!M18</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>14</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>CALCULATION!A19</f>
         <v>3</v>
@@ -49503,8 +49632,14 @@
         <f>CALCULATION!M19</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>CALCULATION!A20</f>
         <v>12</v>
@@ -49537,8 +49672,14 @@
         <f>CALCULATION!M20</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>16</v>
+      </c>
+      <c r="L17" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>CALCULATION!A21</f>
         <v>25</v>
@@ -49571,8 +49712,14 @@
         <f>CALCULATION!M21</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>CALCULATION!A22</f>
         <v>42</v>
@@ -49605,8 +49752,14 @@
         <f>CALCULATION!M22</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>CALCULATION!A23</f>
         <v>60</v>
@@ -49639,8 +49792,14 @@
         <f>CALCULATION!M23</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>19</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>CALCULATION!A24</f>
         <v>28</v>
@@ -49673,8 +49832,14 @@
         <f>CALCULATION!M24</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>20</v>
+      </c>
+      <c r="L21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>CALCULATION!A25</f>
         <v>41</v>
@@ -49707,8 +49872,14 @@
         <f>CALCULATION!M25</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>21</v>
+      </c>
+      <c r="L22" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>CALCULATION!A26</f>
         <v>-</v>
@@ -49741,8 +49912,14 @@
         <f>CALCULATION!M26</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>CALCULATION!A27</f>
         <v>59</v>
@@ -49775,8 +49952,14 @@
         <f>CALCULATION!M27</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>CALCULATION!A28</f>
         <v>34</v>
@@ -49809,8 +49992,14 @@
         <f>CALCULATION!M28</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>24</v>
+      </c>
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>CALCULATION!A29</f>
         <v>14</v>
@@ -49843,8 +50032,14 @@
         <f>CALCULATION!M29</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>25</v>
+      </c>
+      <c r="L26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>CALCULATION!A30</f>
         <v>47</v>
@@ -49877,8 +50072,14 @@
         <f>CALCULATION!M30</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>26</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>CALCULATION!A31</f>
         <v>73</v>
@@ -49911,8 +50112,14 @@
         <f>CALCULATION!M31</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>27</v>
+      </c>
+      <c r="L28" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>CALCULATION!A32</f>
         <v>52</v>
@@ -49945,8 +50152,14 @@
         <f>CALCULATION!M32</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>28</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>CALCULATION!A33</f>
         <v>65</v>
@@ -49955,7 +50168,7 @@
         <f>CALCULATION!B33</f>
         <v>Tb</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C30" s="76" t="str">
         <f>CALCULATION!C33</f>
         <v>Terbium</v>
       </c>
@@ -49979,8 +50192,14 @@
         <f>CALCULATION!M33</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>29</v>
+      </c>
+      <c r="L30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>CALCULATION!A34</f>
         <v>50</v>
@@ -50013,8 +50232,14 @@
         <f>CALCULATION!M34</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>30</v>
+      </c>
+      <c r="L31" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>CALCULATION!A35</f>
         <v>22</v>
@@ -50047,8 +50272,14 @@
         <f>CALCULATION!M35</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>CALCULATION!A36</f>
         <v>74</v>
@@ -50081,8 +50312,14 @@
         <f>CALCULATION!M36</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>CALCULATION!A37</f>
         <v>23</v>
@@ -50115,8 +50352,14 @@
         <f>CALCULATION!M37</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <v>33</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <f>CALCULATION!A38</f>
         <v>39</v>
@@ -50149,8 +50392,14 @@
         <f>CALCULATION!M38</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <v>34</v>
+      </c>
+      <c r="L35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <f>CALCULATION!A39</f>
         <v>30</v>
@@ -50183,8 +50432,14 @@
         <f>CALCULATION!M39</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <v>35</v>
+      </c>
+      <c r="L36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <f>CALCULATION!A40</f>
         <v>40</v>
@@ -50217,15 +50472,18 @@
         <f>CALCULATION!M40</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -50234,6 +50492,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
